--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,35 +895,35 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>-84.210526315789</v>
+        <v>-68.75</v>
       </c>
       <c r="I16" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J16" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K16" s="14">
-        <v>-66.666666666666</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-75</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M16" s="14">
-        <v>-73.076923076923</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.764705882352</v>
+        <v>-89.361702127659</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
         <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G17" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" s="14">
-        <v>-52.380952380952</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="I17" s="15">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J17" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K17" s="14">
-        <v>-35.483870967741</v>
+        <v>-20</v>
       </c>
       <c r="L17" s="14">
-        <v>-52.380952380952</v>
+        <v>-45.098039215686</v>
       </c>
       <c r="M17" s="14">
-        <v>17.647058823529</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-65.517241379310</v>
+        <v>-59.420289855072</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
         <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
         <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
+        <v>-46.153846153846</v>
+      </c>
+      <c r="I18" s="15">
+        <v>9</v>
+      </c>
+      <c r="J18" s="15">
+        <v>18</v>
+      </c>
+      <c r="K18" s="14">
         <v>-50</v>
       </c>
-      <c r="I18" s="15">
-        <v>7</v>
-      </c>
-      <c r="J18" s="15">
-        <v>16</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-56.25</v>
-      </c>
       <c r="L18" s="14">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="M18" s="14">
-        <v>-53.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="N18" s="14">
-        <v>-86.538461538461</v>
+        <v>-83.636363636363</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>-28.571428571428</v>
+        <v>75</v>
       </c>
       <c r="F19" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G19" s="15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>-25</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I19" s="15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J19" s="15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K19" s="14">
-        <v>-21.052631578947</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L19" s="14">
-        <v>-18.918918918918</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="M19" s="14">
-        <v>20</v>
+        <v>35.714285714285</v>
       </c>
       <c r="N19" s="14">
-        <v>7.142857142857</v>
+        <v>26.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,20 +1100,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="15">
         <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>-77.777777777777</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="I20" s="15">
         <v>4</v>
@@ -1131,7 +1131,7 @@
         <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.235294117647</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-56.25</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H21" s="18">
-        <v>-51.086956521739</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="I21" s="17">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="J21" s="17">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="K21" s="18">
-        <v>-40.170940170940</v>
+        <v>-30.534351145038</v>
       </c>
       <c r="L21" s="18">
-        <v>-44.444444444444</v>
+        <v>-39.333333333333</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.315789473684</v>
+        <v>-14.150943396226</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.868217054263</v>
+        <v>-68.292682926829</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="15">
-        <v>2</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>2</v>
@@ -1210,7 +1210,7 @@
         <v>-50</v>
       </c>
       <c r="M22" s="14">
-        <v>-71.428571428571</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
+        <v>3</v>
+      </c>
+      <c r="D23" s="15">
         <v>2</v>
       </c>
-      <c r="D23" s="15">
-        <v>4</v>
-      </c>
       <c r="E23" s="14">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F23" s="15">
         <v>7</v>
       </c>
       <c r="G23" s="15">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H23" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J23" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K23" s="14">
-        <v>-72</v>
+        <v>-62.962962962963</v>
       </c>
       <c r="L23" s="14">
-        <v>-65</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M23" s="14">
-        <v>-36.363636363636</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D24" s="15">
+        <v>20</v>
+      </c>
+      <c r="E24" s="14">
         <v>15</v>
       </c>
-      <c r="E24" s="14">
-        <v>66.666666666666</v>
-      </c>
       <c r="F24" s="15">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="G24" s="15">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H24" s="14">
-        <v>-35.593220338983</v>
+        <v>-8.955223880597</v>
       </c>
       <c r="I24" s="15">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="J24" s="15">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.666666666666</v>
+        <v>-14.736842105263</v>
       </c>
       <c r="L24" s="14">
-        <v>-14.0625</v>
+        <v>-7.954545454545</v>
       </c>
       <c r="M24" s="14">
-        <v>-48.598130841121</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>60</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G25" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H25" s="14">
-        <v>-42.105263157894</v>
+        <v>-12.5</v>
       </c>
       <c r="I25" s="15">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J25" s="15">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K25" s="14">
-        <v>-35</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="L25" s="14">
-        <v>-31.578947368421</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>-66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G26" s="15">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H26" s="14">
-        <v>-46.666666666666</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="I26" s="15">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J26" s="15">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K26" s="14">
-        <v>-40.277777777777</v>
+        <v>-34.523809523809</v>
       </c>
       <c r="L26" s="14">
-        <v>-29.508196721311</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>-12.244897959183</v>
+        <v>-3.508771929824</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,29 +1384,29 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
         <v>0</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
         <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="15">
         <v>9</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>2</v>
       </c>
       <c r="G29" s="15">
         <v>2</v>
       </c>
       <c r="H29" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="15">
         <v>2</v>
       </c>
       <c r="K29" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="14">
+        <v>300</v>
+      </c>
+      <c r="N29" s="14">
         <v>100</v>
-      </c>
-      <c r="N29" s="14">
-        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>2</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,32 +1516,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>2</v>
       </c>
       <c r="G30" s="15">
         <v>2</v>
       </c>
       <c r="H30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" s="15">
         <v>2</v>
       </c>
       <c r="K30" s="14">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N30" s="14">
-        <v>-50</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -925,8 +925,8 @@
       <c r="M15" s="14">
         <v>-50</v>
       </c>
-      <c r="N15" s="13" t="s">
-        <v>21</v>
+      <c r="N15" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
         <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>-68.75</v>
+        <v>-62.5</v>
       </c>
       <c r="I16" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J16" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K16" s="14">
-        <v>-58.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="L16" s="14">
-        <v>-71.428571428571</v>
+        <v>-70</v>
       </c>
       <c r="M16" s="14">
-        <v>-64.285714285714</v>
+        <v>-62.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.361702127659</v>
+        <v>-88.990825688073</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H17" s="14">
-        <v>-40.909090909090</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J17" s="15">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K17" s="14">
-        <v>-20</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="L17" s="14">
-        <v>-45.098039215686</v>
+        <v>-49.206349206349</v>
       </c>
       <c r="M17" s="14">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N17" s="14">
-        <v>-59.420289855072</v>
+        <v>-57.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-46.153846153846</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I18" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K18" s="14">
         <v>-50</v>
       </c>
       <c r="L18" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>-40</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.636363636363</v>
+        <v>-84.375</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>75</v>
+        <v>-37.5</v>
       </c>
       <c r="F19" s="15">
+        <v>21</v>
+      </c>
+      <c r="G19" s="15">
         <v>25</v>
       </c>
-      <c r="G19" s="15">
-        <v>26</v>
-      </c>
       <c r="H19" s="14">
-        <v>-3.846153846153</v>
+        <v>-16</v>
       </c>
       <c r="I19" s="15">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J19" s="15">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K19" s="14">
-        <v>-9.523809523809</v>
+        <v>-12</v>
       </c>
       <c r="L19" s="14">
-        <v>-11.627906976744</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M19" s="14">
-        <v>35.714285714285</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N19" s="14">
-        <v>26.666666666666</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>-88.888888888888</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="15">
         <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L20" s="14">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M20" s="14">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.473684210526</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>28.571428571428</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G21" s="17">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>-41.379310344827</v>
+        <v>-39.240506329113</v>
       </c>
       <c r="I21" s="17">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J21" s="17">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="K21" s="18">
-        <v>-30.534351145038</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="L21" s="18">
-        <v>-39.333333333333</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.150943396226</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.292682926829</v>
+        <v>-67.987804878048</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>3</v>
-      </c>
-      <c r="D23" s="15">
         <v>2</v>
       </c>
-      <c r="E23" s="14">
-        <v>50</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G23" s="15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H23" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J23" s="15">
         <v>27</v>
       </c>
       <c r="K23" s="14">
-        <v>-62.962962962963</v>
+        <v>-51.851851851851</v>
       </c>
       <c r="L23" s="14">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="14">
-        <v>-16.666666666666</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D24" s="15">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E24" s="14">
-        <v>15</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="15">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G24" s="15">
         <v>67</v>
       </c>
       <c r="H24" s="14">
-        <v>-8.955223880597</v>
+        <v>1.492537313432</v>
       </c>
       <c r="I24" s="15">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J24" s="15">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="K24" s="14">
-        <v>-14.736842105263</v>
+        <v>-14.678899082568</v>
       </c>
       <c r="L24" s="14">
-        <v>-7.954545454545</v>
+        <v>-10.576923076923</v>
       </c>
       <c r="M24" s="14">
-        <v>-37.209302325581</v>
+        <v>-37.162162162162</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>11.111111111111</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G25" s="15">
         <v>24</v>
       </c>
       <c r="H25" s="14">
-        <v>-12.5</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J25" s="15">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K25" s="14">
-        <v>-20.689655172413</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="L25" s="14">
-        <v>-17.857142857142</v>
+        <v>-18.75</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-16.666666666666</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G26" s="15">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H26" s="14">
-        <v>-26.829268292682</v>
+        <v>2.702702702702</v>
       </c>
       <c r="I26" s="15">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="J26" s="15">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K26" s="14">
-        <v>-34.523809523809</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="L26" s="14">
-        <v>-16.666666666666</v>
+        <v>-4.054054054054</v>
       </c>
       <c r="M26" s="14">
-        <v>-3.508771929824</v>
+        <v>7.575757575757</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="15">
         <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>300</v>
       </c>
       <c r="N29" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>2</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>200</v>
       </c>
       <c r="N30" s="14">
-        <v>50</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -914,16 +914,16 @@
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="14">
         <v>-33.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N15" s="14">
         <v>100</v>
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>-62.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J16" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>-60</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="L16" s="14">
-        <v>-70</v>
+        <v>-63.414634146341</v>
       </c>
       <c r="M16" s="14">
-        <v>-62.5</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.990825688073</v>
+        <v>-87.288135593220</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>-41.666666666666</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I17" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J17" s="15">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K17" s="14">
-        <v>-25.581395348837</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>-49.206349206349</v>
+        <v>-45.070422535211</v>
       </c>
       <c r="M17" s="14">
-        <v>14.285714285714</v>
+        <v>14.705882352941</v>
       </c>
       <c r="N17" s="14">
-        <v>-57.333333333333</v>
+        <v>-55.172413793103</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-50</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
         <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>-44.444444444444</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J18" s="15">
         <v>20</v>
       </c>
       <c r="K18" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="L18" s="14">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M18" s="14">
-        <v>-41.176470588235</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-84.375</v>
+        <v>-84.810126582278</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
         <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G19" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H19" s="14">
-        <v>-16</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I19" s="15">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J19" s="15">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K19" s="14">
-        <v>-12</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L19" s="14">
-        <v>-15.384615384615</v>
+        <v>-27.536231884058</v>
       </c>
       <c r="M19" s="14">
-        <v>57.142857142857</v>
+        <v>47.058823529411</v>
       </c>
       <c r="N19" s="14">
-        <v>37.5</v>
+        <v>38.888888888888</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,28 +1110,28 @@
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="15">
         <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-44.444444444444</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M20" s="14">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.888888888888</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-45.833333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>-39.240506329113</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="I21" s="17">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="J21" s="17">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="K21" s="18">
-        <v>-32.258064516129</v>
+        <v>-25.748502994012</v>
       </c>
       <c r="L21" s="18">
-        <v>-41.666666666666</v>
+        <v>-41.784037558685</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.764705882352</v>
+        <v>-9.489051094890</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.987804878048</v>
+        <v>-66.933333333333</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M22" s="14">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,13 +1230,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I23" s="15">
         <v>13</v>
@@ -1248,10 +1248,10 @@
         <v>-51.851851851851</v>
       </c>
       <c r="L23" s="14">
-        <v>-50</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" s="15">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
-        <v>-28.571428571428</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="F24" s="15">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G24" s="15">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H24" s="14">
-        <v>1.492537313432</v>
+        <v>-1.388888888888</v>
       </c>
       <c r="I24" s="15">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J24" s="15">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="K24" s="14">
-        <v>-14.678899082568</v>
+        <v>-21.969696969697</v>
       </c>
       <c r="L24" s="14">
-        <v>-10.576923076923</v>
+        <v>-21.969696969697</v>
       </c>
       <c r="M24" s="14">
-        <v>-37.162162162162</v>
+        <v>-36.809815950920</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15">
         <v>3</v>
       </c>
-      <c r="D25" s="15">
-        <v>4</v>
-      </c>
       <c r="E25" s="14">
-        <v>-25</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G25" s="15">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H25" s="14">
-        <v>-4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="I25" s="15">
         <v>26</v>
       </c>
       <c r="J25" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K25" s="14">
-        <v>-21.212121212121</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L25" s="14">
-        <v>-18.75</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
         <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>166.666666666667</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="15">
         <v>38</v>
       </c>
       <c r="G26" s="15">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H26" s="14">
-        <v>2.702702702702</v>
+        <v>15.151515151515</v>
       </c>
       <c r="I26" s="15">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="J26" s="15">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K26" s="14">
-        <v>-21.111111111111</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L26" s="14">
-        <v>-4.054054054054</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M26" s="14">
-        <v>7.575757575757</v>
+        <v>19.402985074626</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>-25</v>
+        <v>250</v>
       </c>
       <c r="I28" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J28" s="15">
         <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="15">
         <v>2</v>
       </c>
-      <c r="G29" s="15">
-        <v>2</v>
-      </c>
-      <c r="H29" s="14">
-        <v>0</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="15">
         <v>4</v>
@@ -1497,10 +1497,10 @@
         <v>21</v>
       </c>
       <c r="M29" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N29" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="15">
         <v>2</v>
       </c>
-      <c r="G30" s="15">
-        <v>2</v>
-      </c>
-      <c r="H30" s="14">
-        <v>0</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="15">
         <v>3</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N30" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="15">
-        <v>1</v>
-      </c>
-      <c r="H33" s="14">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="N15" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-75</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-27.272727272727</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K16" s="14">
-        <v>-51.612903225806</v>
+        <v>-54.285714285714</v>
       </c>
       <c r="L16" s="14">
-        <v>-63.414634146341</v>
+        <v>-67.346938775510</v>
       </c>
       <c r="M16" s="14">
-        <v>-58.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.288135593220</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>200</v>
+        <v>-62.5</v>
       </c>
       <c r="F17" s="15">
         <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H17" s="14">
-        <v>5.555555555555</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I17" s="15">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J17" s="15">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K17" s="14">
-        <v>-13.333333333333</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="L17" s="14">
-        <v>-45.070422535211</v>
+        <v>-48.75</v>
       </c>
       <c r="M17" s="14">
-        <v>14.705882352941</v>
+        <v>20.588235294117</v>
       </c>
       <c r="N17" s="14">
-        <v>-55.172413793103</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
       </c>
       <c r="F18" s="15">
+        <v>6</v>
+      </c>
+      <c r="G18" s="15">
         <v>5</v>
       </c>
-      <c r="G18" s="15">
-        <v>6</v>
-      </c>
       <c r="H18" s="14">
-        <v>-16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="I18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="14">
-        <v>-40</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="L18" s="14">
-        <v>-14.285714285714</v>
+        <v>-18.75</v>
       </c>
       <c r="M18" s="14">
-        <v>-33.333333333333</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N18" s="14">
-        <v>-84.810126582278</v>
+        <v>-85.227272727272</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1066,39 +1066,39 @@
         <v>-25</v>
       </c>
       <c r="F19" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" s="14">
-        <v>-11.111111111111</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="I19" s="15">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J19" s="15">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="K19" s="14">
-        <v>-13.793103448275</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="L19" s="14">
-        <v>-27.536231884058</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M19" s="14">
-        <v>47.058823529411</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N19" s="14">
-        <v>38.888888888888</v>
+        <v>27.272727272727</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1109,11 +1109,11 @@
       <c r="F20" s="15">
         <v>2</v>
       </c>
-      <c r="G20" s="15">
-        <v>2</v>
-      </c>
-      <c r="H20" s="14">
-        <v>0</v>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="15">
         <v>6</v>
@@ -1125,13 +1125,13 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="M20" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.235294117647</v>
+        <v>-89.090909090909</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.121212121212</v>
+        <v>-12.676056338028</v>
       </c>
       <c r="I21" s="17">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J21" s="17">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.748502994012</v>
+        <v>-28.191489361702</v>
       </c>
       <c r="L21" s="18">
-        <v>-41.784037558685</v>
+        <v>-44.214876033057</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.489051094890</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.933333333333</v>
+        <v>-68.457943925233</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1201,16 +1201,16 @@
         <v>2</v>
       </c>
       <c r="J22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="14">
         <v>-60</v>
       </c>
       <c r="M22" s="14">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="15">
+        <v>2</v>
+      </c>
+      <c r="D23" s="15">
+        <v>4</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-50</v>
       </c>
       <c r="F23" s="15">
         <v>8</v>
@@ -1239,19 +1239,19 @@
         <v>33.333333333333</v>
       </c>
       <c r="I23" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J23" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K23" s="14">
-        <v>-51.851851851851</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="L23" s="14">
-        <v>-56.666666666666</v>
+        <v>-60.526315789473</v>
       </c>
       <c r="M23" s="14">
-        <v>0</v>
+        <v>15.384615384615</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>8</v>
+      </c>
+      <c r="D24" s="15">
         <v>11</v>
       </c>
-      <c r="D24" s="15">
-        <v>23</v>
-      </c>
       <c r="E24" s="14">
-        <v>-52.173913043478</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F24" s="15">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="G24" s="15">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H24" s="14">
-        <v>-1.388888888888</v>
+        <v>-22.058823529411</v>
       </c>
       <c r="I24" s="15">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="J24" s="15">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="K24" s="14">
-        <v>-21.969696969697</v>
+        <v>-22.377622377622</v>
       </c>
       <c r="L24" s="14">
-        <v>-21.969696969697</v>
+        <v>-27.450980392156</v>
       </c>
       <c r="M24" s="14">
-        <v>-36.809815950920</v>
+        <v>-37.988826815642</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1312,25 +1312,25 @@
         <v>-66.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G25" s="15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H25" s="14">
-        <v>0</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I25" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J25" s="15">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K25" s="14">
-        <v>-27.777777777777</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L25" s="14">
-        <v>-23.529411764705</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G26" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H26" s="14">
-        <v>15.151515151515</v>
+        <v>19.444444444444</v>
       </c>
       <c r="I26" s="15">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J26" s="15">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K26" s="14">
-        <v>-16.666666666666</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L26" s="14">
-        <v>-9.090909090909</v>
+        <v>-14.563106796116</v>
       </c>
       <c r="M26" s="14">
-        <v>19.402985074626</v>
+        <v>17.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="15">
         <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>133.333333333333</v>
+        <v>87.5</v>
       </c>
       <c r="L28" s="14">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>0</v>
       </c>
       <c r="N29" s="14">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="14">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -914,10 +914,10 @@
         <v>3</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>-35.714285714285</v>
+        <v>-56.25</v>
       </c>
       <c r="I16" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K16" s="14">
-        <v>-54.285714285714</v>
+        <v>-55</v>
       </c>
       <c r="L16" s="14">
-        <v>-67.346938775510</v>
+        <v>-66.037735849056</v>
       </c>
       <c r="M16" s="14">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.235294117647</v>
+        <v>-87.837837837837</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
-      </c>
-      <c r="D17" s="15">
-        <v>8</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-62.5</v>
+        <v>12</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G17" s="15">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>-13.636363636363</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I17" s="15">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="J17" s="15">
         <v>53</v>
       </c>
       <c r="K17" s="14">
-        <v>-22.641509433962</v>
+        <v>1.886792452830</v>
       </c>
       <c r="L17" s="14">
-        <v>-48.75</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="M17" s="14">
-        <v>20.588235294117</v>
+        <v>35</v>
       </c>
       <c r="N17" s="14">
-        <v>-59</v>
+        <v>-49.532710280373</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" s="15">
         <v>6</v>
@@ -1034,22 +1034,22 @@
         <v>20</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J18" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K18" s="14">
-        <v>-38.095238095238</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L18" s="14">
-        <v>-18.75</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M18" s="14">
-        <v>-31.578947368421</v>
+        <v>-20</v>
       </c>
       <c r="N18" s="14">
-        <v>-85.227272727272</v>
+        <v>-83.505154639175</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-25</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F19" s="15">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G19" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H19" s="14">
-        <v>-10.714285714285</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="I19" s="15">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J19" s="15">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K19" s="14">
-        <v>-15.151515151515</v>
+        <v>-21.917808219178</v>
       </c>
       <c r="L19" s="14">
-        <v>-27.272727272727</v>
+        <v>-35.227272727272</v>
       </c>
       <c r="M19" s="14">
-        <v>55.555555555555</v>
+        <v>46.153846153846</v>
       </c>
       <c r="N19" s="14">
-        <v>27.272727272727</v>
+        <v>23.913043478260</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="15">
+        <v>2</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>100</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="14">
+        <v>300</v>
       </c>
       <c r="I20" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="14">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="14">
-        <v>-62.5</v>
+        <v>-60</v>
       </c>
       <c r="M20" s="14">
-        <v>-33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.090909090909</v>
+        <v>-85.964912280701</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.857142857142</v>
+        <v>31.25</v>
       </c>
       <c r="F21" s="17">
         <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.676056338028</v>
+        <v>-15.068493150684</v>
       </c>
       <c r="I21" s="17">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="J21" s="17">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="K21" s="18">
-        <v>-28.191489361702</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L21" s="18">
-        <v>-44.214876033057</v>
+        <v>-43.272727272727</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.896551724137</v>
+        <v>-0.636942675159</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.457943925233</v>
+        <v>-66.086956521739</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="15">
         <v>1</v>
       </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="15">
         <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M22" s="14">
-        <v>-81.818181818181</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>2</v>
       </c>
       <c r="D23" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G23" s="15">
         <v>6</v>
       </c>
       <c r="H23" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J23" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K23" s="14">
-        <v>-51.612903225806</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="L23" s="14">
-        <v>-60.526315789473</v>
+        <v>-58.536585365853</v>
       </c>
       <c r="M23" s="14">
-        <v>15.384615384615</v>
+        <v>6.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.272727272727</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F24" s="15">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G24" s="15">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H24" s="14">
-        <v>-22.058823529411</v>
+        <v>-28.985507246376</v>
       </c>
       <c r="I24" s="15">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="J24" s="15">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="K24" s="14">
-        <v>-22.377622377622</v>
+        <v>-20.121951219512</v>
       </c>
       <c r="L24" s="14">
-        <v>-27.450980392156</v>
+        <v>-23.391812865497</v>
       </c>
       <c r="M24" s="14">
-        <v>-37.988826815642</v>
+        <v>-32.474226804123</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" s="14">
-        <v>-66.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G25" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H25" s="14">
-        <v>-26.315789473684</v>
+        <v>-25</v>
       </c>
       <c r="I25" s="15">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J25" s="15">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.769230769230</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="L25" s="14">
-        <v>-30.769230769230</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>-33.333333333333</v>
+        <v>142.857142857143</v>
       </c>
       <c r="F26" s="15">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G26" s="15">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H26" s="14">
-        <v>19.444444444444</v>
+        <v>67.741935483871</v>
       </c>
       <c r="I26" s="15">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="J26" s="15">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K26" s="14">
-        <v>-18.518518518518</v>
+        <v>-7.826086956521</v>
       </c>
       <c r="L26" s="14">
-        <v>-14.563106796116</v>
+        <v>-18.461538461538</v>
       </c>
       <c r="M26" s="14">
-        <v>17.333333333333</v>
+        <v>29.268292682926</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-50</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I28" s="15">
         <v>15</v>
@@ -1466,17 +1466,17 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="15">
         <v>1</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="15">
-        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1493,31 +1493,31 @@
       <c r="K29" s="14">
         <v>100</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="14">
+        <v>300</v>
       </c>
       <c r="M29" s="14">
         <v>0</v>
       </c>
       <c r="N29" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="15">
         <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="15">
-        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1534,14 +1534,14 @@
       <c r="K30" s="14">
         <v>50</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="14">
+        <v>200</v>
       </c>
       <c r="M30" s="14">
         <v>0</v>
       </c>
       <c r="N30" s="14">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
       </c>
       <c r="E15" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="N15" s="14">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" s="15">
         <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-60</v>
+        <v>20</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>-56.25</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K16" s="14">
-        <v>-55</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-66.037735849056</v>
+        <v>-58.620689655172</v>
       </c>
       <c r="M16" s="14">
-        <v>-57.142857142857</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.837837837837</v>
+        <v>-85.093167701863</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>12</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="D17" s="15">
+        <v>7</v>
+      </c>
+      <c r="E17" s="14">
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H17" s="14">
-        <v>44.444444444444</v>
+        <v>70.588235294117</v>
       </c>
       <c r="I17" s="15">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J17" s="15">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K17" s="14">
-        <v>1.886792452830</v>
+        <v>1.666666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>-41.935483870967</v>
+        <v>-43.518518518518</v>
       </c>
       <c r="M17" s="14">
-        <v>35</v>
+        <v>32.608695652173</v>
       </c>
       <c r="N17" s="14">
-        <v>-49.532710280373</v>
+        <v>-47.863247863247</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
       <c r="E18" s="14">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
         <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K18" s="14">
-        <v>-30.434782608695</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="L18" s="14">
-        <v>-5.882352941176</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M18" s="14">
-        <v>-20</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.505154639175</v>
+        <v>-83.495145631068</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>-71.428571428571</v>
+        <v>-60</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>-41.935483870967</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="I19" s="15">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J19" s="15">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K19" s="14">
-        <v>-21.917808219178</v>
+        <v>-26.506024096385</v>
       </c>
       <c r="L19" s="14">
-        <v>-35.227272727272</v>
+        <v>-39.603960396039</v>
       </c>
       <c r="M19" s="14">
-        <v>46.153846153846</v>
+        <v>48.780487804878</v>
       </c>
       <c r="N19" s="14">
-        <v>23.913043478260</v>
+        <v>15.094339622641</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
         <v>8</v>
       </c>
       <c r="J20" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M20" s="14">
         <v>-11.111111111111</v>
       </c>
       <c r="N20" s="14">
-        <v>-85.964912280701</v>
+        <v>-88.059701492537</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>31.25</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.068493150684</v>
+        <v>-11.688311688311</v>
       </c>
       <c r="I21" s="17">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="J21" s="17">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.529411764705</v>
+        <v>-24.568965517241</v>
       </c>
       <c r="L21" s="18">
-        <v>-43.272727272727</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.636942675159</v>
+        <v>2.941176470588</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.086956521739</v>
+        <v>-65.618860510805</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="15">
         <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="14">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M22" s="14">
-        <v>-72.727272727272</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F23" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G23" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I23" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J23" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K23" s="14">
-        <v>-48.484848484848</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="L23" s="14">
-        <v>-58.536585365853</v>
+        <v>-48.837209302325</v>
       </c>
       <c r="M23" s="14">
-        <v>6.25</v>
+        <v>29.411764705882</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D24" s="15">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E24" s="14">
-        <v>-4.761904761904</v>
+        <v>75</v>
       </c>
       <c r="F24" s="15">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G24" s="15">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H24" s="14">
-        <v>-28.985507246376</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I24" s="15">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="J24" s="15">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K24" s="14">
-        <v>-20.121951219512</v>
+        <v>-15.116279069767</v>
       </c>
       <c r="L24" s="14">
-        <v>-23.391812865497</v>
+        <v>-27</v>
       </c>
       <c r="M24" s="14">
-        <v>-32.474226804123</v>
+        <v>-32.407407407407</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>16.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H25" s="14">
-        <v>-25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I25" s="15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J25" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K25" s="14">
-        <v>-24.444444444444</v>
+        <v>-25.531914893617</v>
       </c>
       <c r="L25" s="14">
-        <v>-19.047619047619</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>142.857142857143</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G26" s="15">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H26" s="14">
-        <v>67.741935483871</v>
+        <v>10.810810810810</v>
       </c>
       <c r="I26" s="15">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J26" s="15">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="K26" s="14">
-        <v>-7.826086956521</v>
+        <v>-12.598425196850</v>
       </c>
       <c r="L26" s="14">
-        <v>-18.461538461538</v>
+        <v>-22.377622377622</v>
       </c>
       <c r="M26" s="14">
-        <v>29.268292682926</v>
+        <v>15.625</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>87.5</v>
+        <v>77.777777777777</v>
       </c>
       <c r="L28" s="14">
-        <v>36.363636363636</v>
+        <v>45.454545454545</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="15">
         <v>2</v>
       </c>
       <c r="K29" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L29" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M29" s="14">
         <v>0</v>
       </c>
       <c r="N29" s="14">
-        <v>-50</v>
+        <v>-58.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="15">
         <v>2</v>
       </c>
       <c r="K30" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L30" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M30" s="14">
         <v>0</v>
       </c>
       <c r="N30" s="14">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F16" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>-26.666666666666</v>
+        <v>-18.75</v>
       </c>
       <c r="I16" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J16" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K16" s="14">
-        <v>-46.666666666666</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="L16" s="14">
-        <v>-58.620689655172</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="M16" s="14">
-        <v>-47.826086956521</v>
+        <v>-47.169811320754</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.093167701863</v>
+        <v>-83.815028901734</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>6</v>
+      </c>
+      <c r="D17" s="15">
         <v>8</v>
       </c>
-      <c r="D17" s="15">
-        <v>7</v>
-      </c>
       <c r="E17" s="14">
-        <v>14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" s="15">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H17" s="14">
-        <v>70.588235294117</v>
+        <v>30.434782608695</v>
       </c>
       <c r="I17" s="15">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J17" s="15">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="K17" s="14">
-        <v>1.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>-43.518518518518</v>
+        <v>-40.869565217391</v>
       </c>
       <c r="M17" s="14">
-        <v>32.608695652173</v>
+        <v>28.301886792452</v>
       </c>
       <c r="N17" s="14">
-        <v>-47.863247863247</v>
+        <v>-45.161290322580</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I18" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J18" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K18" s="14">
-        <v>-34.615384615384</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="L18" s="14">
-        <v>-10.526315789473</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M18" s="14">
-        <v>-19.047619047619</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.495145631068</v>
+        <v>-81.981981981982</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-60</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="15">
         <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="14">
-        <v>-48.484848484848</v>
+        <v>-46.875</v>
       </c>
       <c r="I19" s="15">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J19" s="15">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K19" s="14">
-        <v>-26.506024096385</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>-39.603960396039</v>
+        <v>-39.449541284403</v>
       </c>
       <c r="M19" s="14">
-        <v>48.780487804878</v>
+        <v>43.478260869565</v>
       </c>
       <c r="N19" s="14">
-        <v>15.094339622641</v>
+        <v>15.789473684210</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,28 +1110,28 @@
         <v>3</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K20" s="14">
-        <v>-33.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L20" s="14">
         <v>-66.666666666666</v>
       </c>
       <c r="M20" s="14">
-        <v>-11.111111111111</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.059701492537</v>
+        <v>-86.764705882352</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.688311688311</v>
+        <v>-16.091954022988</v>
       </c>
       <c r="I21" s="17">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="J21" s="17">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.568965517241</v>
+        <v>-23.228346456692</v>
       </c>
       <c r="L21" s="18">
-        <v>-44.444444444444</v>
+        <v>-42.982456140350</v>
       </c>
       <c r="M21" s="18">
-        <v>2.941176470588</v>
+        <v>-0.510204081632</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.618860510805</v>
+        <v>-63.955637707948</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15">
+        <v>3</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
         <v>4</v>
       </c>
       <c r="J22" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="14">
-        <v>-42.857142857142</v>
+        <v>-60</v>
       </c>
       <c r="M22" s="14">
         <v>-66.666666666666</v>
@@ -1224,34 +1224,34 @@
         <v>5</v>
       </c>
       <c r="D23" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
+        <v>150</v>
+      </c>
+      <c r="F23" s="15">
+        <v>15</v>
+      </c>
+      <c r="G23" s="15">
+        <v>12</v>
+      </c>
+      <c r="H23" s="14">
         <v>25</v>
       </c>
-      <c r="F23" s="15">
-        <v>9</v>
-      </c>
-      <c r="G23" s="15">
-        <v>10</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-10</v>
-      </c>
       <c r="I23" s="15">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J23" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K23" s="14">
-        <v>-40.540540540540</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="L23" s="14">
-        <v>-48.837209302325</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="M23" s="14">
-        <v>29.411764705882</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G24" s="15">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H24" s="14">
-        <v>-14.285714285714</v>
+        <v>5.357142857142</v>
       </c>
       <c r="I24" s="15">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="J24" s="15">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="K24" s="14">
-        <v>-15.116279069767</v>
+        <v>-13.829787234042</v>
       </c>
       <c r="L24" s="14">
-        <v>-27</v>
+        <v>-24.651162790697</v>
       </c>
       <c r="M24" s="14">
-        <v>-32.407407407407</v>
+        <v>-28.318584070796</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" s="14">
-        <v>-28.571428571428</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J25" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K25" s="14">
-        <v>-25.531914893617</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="L25" s="14">
-        <v>-28.571428571428</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>5.555555555555</v>
       </c>
       <c r="F26" s="15">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G26" s="15">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H26" s="14">
-        <v>10.810810810810</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="J26" s="15">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="K26" s="14">
-        <v>-12.598425196850</v>
+        <v>-11.034482758620</v>
       </c>
       <c r="L26" s="14">
-        <v>-22.377622377622</v>
+        <v>-22.754491017964</v>
       </c>
       <c r="M26" s="14">
-        <v>15.625</v>
+        <v>24.038461538461</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
@@ -1412,7 +1412,7 @@
         <v>-16.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>6</v>
@@ -1444,16 +1444,16 @@
         <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J28" s="15">
         <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>77.777777777777</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>45.454545454545</v>
+        <v>75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,35 +1466,35 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="15">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="15">
         <v>2</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="14">
+        <v>100</v>
       </c>
       <c r="I29" s="15">
         <v>5</v>
       </c>
       <c r="J29" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="14">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L29" s="14">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="M29" s="14">
         <v>0</v>
@@ -1507,35 +1507,35 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="15">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="15">
         <v>2</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>100</v>
       </c>
       <c r="I30" s="15">
         <v>4</v>
       </c>
       <c r="J30" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="14">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="14">
-        <v>300</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M30" s="14">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J15" s="15">
         <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
         <v>3</v>
       </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
       <c r="E16" s="14">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
         <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>-18.75</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J16" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K16" s="14">
-        <v>-40.425531914893</v>
+        <v>-42</v>
       </c>
       <c r="L16" s="14">
-        <v>-54.838709677419</v>
+        <v>-54.6875</v>
       </c>
       <c r="M16" s="14">
-        <v>-47.169811320754</v>
+        <v>-51.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.815028901734</v>
+        <v>-84.239130434782</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F17" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G17" s="15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>30.434782608695</v>
+        <v>73.684210526315</v>
       </c>
       <c r="I17" s="15">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J17" s="15">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>-40.869565217391</v>
+        <v>-38.016528925619</v>
       </c>
       <c r="M17" s="14">
-        <v>28.301886792452</v>
+        <v>29.310344827586</v>
       </c>
       <c r="N17" s="14">
-        <v>-45.161290322580</v>
+        <v>-46.428571428571</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
         <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-11.111111111111</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I18" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>-31.034482758620</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="14">
-        <v>-4.761904761904</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M18" s="14">
-        <v>-16.666666666666</v>
+        <v>-4</v>
       </c>
       <c r="N18" s="14">
-        <v>-81.981981981982</v>
+        <v>-80.645161290322</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>-14.285714285714</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F19" s="15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G19" s="15">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>-46.875</v>
+        <v>-43.243243243243</v>
       </c>
       <c r="I19" s="15">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="J19" s="15">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="K19" s="14">
-        <v>-26.666666666666</v>
+        <v>-27.184466019417</v>
       </c>
       <c r="L19" s="14">
-        <v>-39.449541284403</v>
+        <v>-39.516129032258</v>
       </c>
       <c r="M19" s="14">
-        <v>43.478260869565</v>
+        <v>56.25</v>
       </c>
       <c r="N19" s="14">
-        <v>15.789473684210</v>
+        <v>2.739726027397</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" s="14">
-        <v>-35.714285714285</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-66.666666666666</v>
+        <v>-65.517241379310</v>
       </c>
       <c r="M20" s="14">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-86.764705882352</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
         <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.636363636363</v>
+        <v>4.545454545454</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="G21" s="17">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.091954022988</v>
+        <v>-3.409090909090</v>
       </c>
       <c r="I21" s="17">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="J21" s="17">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.228346456692</v>
+        <v>-20.652173913043</v>
       </c>
       <c r="L21" s="18">
-        <v>-42.982456140350</v>
+        <v>-40.489130434782</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.510204081632</v>
+        <v>3.301886792452</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.955637707948</v>
+        <v>-63.801652892562</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
         <v>-100</v>
@@ -1198,19 +1198,19 @@
         <v>-50</v>
       </c>
       <c r="I22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L22" s="14">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="14">
-        <v>-66.666666666666</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>5</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
         <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>150</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G23" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H23" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I23" s="15">
         <v>28</v>
       </c>
       <c r="J23" s="15">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K23" s="14">
-        <v>-28.205128205128</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="L23" s="14">
-        <v>-39.130434782608</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="M23" s="14">
         <v>33.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>0</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F24" s="15">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G24" s="15">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H24" s="14">
-        <v>5.357142857142</v>
+        <v>5.172413793103</v>
       </c>
       <c r="I24" s="15">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="J24" s="15">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="K24" s="14">
-        <v>-13.829787234042</v>
+        <v>-14.427860696517</v>
       </c>
       <c r="L24" s="14">
-        <v>-24.651162790697</v>
+        <v>-26.495726495726</v>
       </c>
       <c r="M24" s="14">
-        <v>-28.318584070796</v>
+        <v>-31.2</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>3</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="15">
         <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>-25</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="14">
-        <v>-20</v>
+        <v>-31.25</v>
       </c>
       <c r="I25" s="15">
         <v>38</v>
       </c>
       <c r="J25" s="15">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K25" s="14">
-        <v>-25.490196078431</v>
+        <v>-30.909090909090</v>
       </c>
       <c r="L25" s="14">
-        <v>-29.629629629629</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E26" s="14">
-        <v>5.555555555555</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="15">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G26" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>-1.886792452830</v>
       </c>
       <c r="I26" s="15">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="J26" s="15">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="K26" s="14">
-        <v>-11.034482758620</v>
+        <v>-12.422360248447</v>
       </c>
       <c r="L26" s="14">
-        <v>-22.754491017964</v>
+        <v>-21.229050279329</v>
       </c>
       <c r="M26" s="14">
-        <v>24.038461538461</v>
+        <v>28.181818181818</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>100</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
         <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L28" s="14">
-        <v>75</v>
+        <v>53.846153846153</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="15">
         <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="15">
-        <v>2</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
       </c>
       <c r="H29" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="15">
         <v>5</v>
@@ -1497,7 +1497,7 @@
         <v>25</v>
       </c>
       <c r="M29" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N29" s="14">
         <v>-58.333333333333</v>
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="15">
         <v>1</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="15">
-        <v>2</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
       </c>
       <c r="H30" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="15">
         <v>4</v>
@@ -1538,7 +1538,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="M30" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N30" s="14">
         <v>-66.666666666666</v>

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="I15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="15">
         <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N15" s="14">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -943,31 +943,31 @@
         <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
+        <v>12</v>
+      </c>
+      <c r="G16" s="15">
         <v>13</v>
       </c>
-      <c r="G16" s="15">
-        <v>15</v>
-      </c>
       <c r="H16" s="14">
-        <v>-13.333333333333</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I16" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J16" s="15">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K16" s="14">
-        <v>-42</v>
+        <v>-43.396226415094</v>
       </c>
       <c r="L16" s="14">
-        <v>-54.6875</v>
+        <v>-55.882352941176</v>
       </c>
       <c r="M16" s="14">
-        <v>-51.666666666666</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.239130434782</v>
+        <v>-84.693877551020</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
         <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F17" s="15">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H17" s="14">
-        <v>73.684210526315</v>
+        <v>17.391304347826</v>
       </c>
       <c r="I17" s="15">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J17" s="15">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K17" s="14">
-        <v>4.166666666666</v>
+        <v>6.578947368421</v>
       </c>
       <c r="L17" s="14">
-        <v>-38.016528925619</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M17" s="14">
-        <v>29.310344827586</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N17" s="14">
-        <v>-46.428571428571</v>
+        <v>-48.076923076923</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>22.222222222222</v>
+        <v>40</v>
       </c>
       <c r="I18" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J18" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14">
-        <v>-20</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L18" s="14">
-        <v>9.090909090909</v>
+        <v>25</v>
       </c>
       <c r="M18" s="14">
-        <v>-4</v>
+        <v>3.448275862068</v>
       </c>
       <c r="N18" s="14">
-        <v>-80.645161290322</v>
+        <v>-77.099236641221</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-30.769230769230</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G19" s="15">
         <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>-43.243243243243</v>
+        <v>-37.837837837837</v>
       </c>
       <c r="I19" s="15">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J19" s="15">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K19" s="14">
-        <v>-27.184466019417</v>
+        <v>-28.181818181818</v>
       </c>
       <c r="L19" s="14">
-        <v>-39.516129032258</v>
+        <v>-42.335766423357</v>
       </c>
       <c r="M19" s="14">
-        <v>56.25</v>
+        <v>49.056603773584</v>
       </c>
       <c r="N19" s="14">
-        <v>2.739726027397</v>
+        <v>1.282051282051</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
         <v>4</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I20" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K20" s="14">
-        <v>-33.333333333333</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="L20" s="14">
-        <v>-65.517241379310</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M20" s="14">
-        <v>-16.666666666666</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-86.666666666666</v>
+        <v>-86.25</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,51 +1142,51 @@
         <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>4.545454545454</v>
+        <v>21.052631578947</v>
       </c>
       <c r="F21" s="17">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.409090909090</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I21" s="17">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="J21" s="17">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.652173913043</v>
+        <v>-19.322033898305</v>
       </c>
       <c r="L21" s="18">
-        <v>-40.489130434782</v>
+        <v>-39.898989898989</v>
       </c>
       <c r="M21" s="18">
-        <v>3.301886792452</v>
+        <v>3.930131004366</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.801652892562</v>
+        <v>-63.440860215053</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="15">
         <v>1</v>
       </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
@@ -1198,19 +1198,19 @@
         <v>-50</v>
       </c>
       <c r="I22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="15">
         <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="M22" s="14">
-        <v>-64.285714285714</v>
+        <v>-62.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>2</v>
       </c>
       <c r="D23" s="15">
         <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
         <v>13</v>
@@ -1239,19 +1239,19 @@
         <v>30</v>
       </c>
       <c r="I23" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J23" s="15">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K23" s="14">
-        <v>-31.707317073170</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="L23" s="14">
-        <v>-40.425531914893</v>
+        <v>-43.396226415094</v>
       </c>
       <c r="M23" s="14">
-        <v>33.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14">
-        <v>-23.076923076923</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F24" s="15">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G24" s="15">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H24" s="14">
-        <v>5.172413793103</v>
+        <v>14.583333333333</v>
       </c>
       <c r="I24" s="15">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="J24" s="15">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="K24" s="14">
-        <v>-14.427860696517</v>
+        <v>-11.792452830188</v>
       </c>
       <c r="L24" s="14">
-        <v>-26.495726495726</v>
+        <v>-26.377952755905</v>
       </c>
       <c r="M24" s="14">
-        <v>-31.2</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="15">
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H25" s="14">
-        <v>-31.25</v>
+        <v>-60</v>
       </c>
       <c r="I25" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J25" s="15">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.909090909090</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L25" s="14">
-        <v>-38.709677419354</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>8</v>
+      </c>
+      <c r="D26" s="15">
         <v>12</v>
       </c>
-      <c r="D26" s="15">
-        <v>16</v>
-      </c>
       <c r="E26" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G26" s="15">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H26" s="14">
-        <v>-1.886792452830</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="I26" s="15">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="J26" s="15">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="K26" s="14">
-        <v>-12.422360248447</v>
+        <v>-13.294797687861</v>
       </c>
       <c r="L26" s="14">
-        <v>-21.229050279329</v>
+        <v>-23.857868020304</v>
       </c>
       <c r="M26" s="14">
-        <v>28.181818181818</v>
+        <v>26.050420168067</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
+        <v>5</v>
+      </c>
+      <c r="G27" s="15">
         <v>2</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>4</v>
-      </c>
-      <c r="G27" s="15">
-        <v>3</v>
-      </c>
       <c r="H27" s="14">
-        <v>33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="15">
         <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L27" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F28" s="15">
         <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
         <v>20</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L28" s="14">
-        <v>53.846153846153</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>66.666666666666</v>
       </c>
       <c r="L29" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M29" s="14">
         <v>-16.666666666666</v>
       </c>
       <c r="N29" s="14">
-        <v>-58.333333333333</v>
+        <v>-64.285714285714</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L30" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M30" s="14">
         <v>-20</v>
       </c>
       <c r="N30" s="14">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15">
         <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
         <v>133.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
+        <v>9</v>
+      </c>
+      <c r="G16" s="15">
         <v>12</v>
       </c>
-      <c r="G16" s="15">
-        <v>13</v>
-      </c>
       <c r="H16" s="14">
-        <v>-7.692307692307</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J16" s="15">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K16" s="14">
-        <v>-43.396226415094</v>
+        <v>-40.350877192982</v>
       </c>
       <c r="L16" s="14">
-        <v>-55.882352941176</v>
+        <v>-52.777777777777</v>
       </c>
       <c r="M16" s="14">
-        <v>-52.380952380952</v>
+        <v>-49.253731343283</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.693877551020</v>
+        <v>-84.821428571428</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E17" s="14">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>27</v>
       </c>
       <c r="G17" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H17" s="14">
-        <v>17.391304347826</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I17" s="15">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J17" s="15">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K17" s="14">
-        <v>6.578947368421</v>
+        <v>4.651162790697</v>
       </c>
       <c r="L17" s="14">
-        <v>-35.714285714285</v>
+        <v>-33.823529411764</v>
       </c>
       <c r="M17" s="14">
-        <v>28.571428571428</v>
+        <v>30.434782608695</v>
       </c>
       <c r="N17" s="14">
-        <v>-48.076923076923</v>
+        <v>-47.368421052631</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="15">
         <v>14</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J18" s="15">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K18" s="14">
-        <v>-9.090909090909</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="L18" s="14">
-        <v>25</v>
+        <v>14.814814814814</v>
       </c>
       <c r="M18" s="14">
-        <v>3.448275862068</v>
+        <v>3.333333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-77.099236641221</v>
+        <v>-77.697841726618</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F19" s="15">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G19" s="15">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H19" s="14">
-        <v>-37.837837837837</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I19" s="15">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J19" s="15">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K19" s="14">
-        <v>-28.181818181818</v>
+        <v>-23.728813559322</v>
       </c>
       <c r="L19" s="14">
-        <v>-42.335766423357</v>
+        <v>-40.397350993377</v>
       </c>
       <c r="M19" s="14">
-        <v>49.056603773584</v>
+        <v>55.172413793103</v>
       </c>
       <c r="N19" s="14">
-        <v>1.282051282051</v>
+        <v>9.756097560975</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="15">
         <v>4</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H20" s="14">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="I20" s="15">
+        <v>12</v>
+      </c>
+      <c r="J20" s="15">
+        <v>21</v>
+      </c>
+      <c r="K20" s="14">
         <v>-42.857142857142</v>
       </c>
-      <c r="I20" s="15">
-        <v>11</v>
-      </c>
-      <c r="J20" s="15">
-        <v>17</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-35.294117647058</v>
-      </c>
       <c r="L20" s="14">
-        <v>-66.666666666666</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="M20" s="14">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-86.25</v>
+        <v>-86.206896551724</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>21.052631578947</v>
+        <v>-15.625</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G21" s="17">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.692307692307</v>
+        <v>-8.421052631578</v>
       </c>
       <c r="I21" s="17">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="J21" s="17">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.322033898305</v>
+        <v>-19.266055045871</v>
       </c>
       <c r="L21" s="18">
-        <v>-39.898989898989</v>
+        <v>-39.030023094688</v>
       </c>
       <c r="M21" s="18">
-        <v>3.930131004366</v>
+        <v>7.317073170731</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.440860215053</v>
+        <v>-63.179916317991</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="15">
         <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="14">
         <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G23" s="15">
         <v>10</v>
       </c>
       <c r="H23" s="14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I23" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J23" s="15">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K23" s="14">
-        <v>-30.232558139534</v>
+        <v>-27.659574468085</v>
       </c>
       <c r="L23" s="14">
-        <v>-43.396226415094</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="M23" s="14">
-        <v>42.857142857142</v>
+        <v>41.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>27</v>
+      </c>
+      <c r="D24" s="15">
         <v>15</v>
       </c>
-      <c r="D24" s="15">
-        <v>11</v>
-      </c>
       <c r="E24" s="14">
-        <v>36.363636363636</v>
+        <v>80</v>
       </c>
       <c r="F24" s="15">
+        <v>68</v>
+      </c>
+      <c r="G24" s="15">
         <v>55</v>
       </c>
-      <c r="G24" s="15">
-        <v>48</v>
-      </c>
       <c r="H24" s="14">
-        <v>14.583333333333</v>
+        <v>23.636363636363</v>
       </c>
       <c r="I24" s="15">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="J24" s="15">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="K24" s="14">
-        <v>-11.792452830188</v>
+        <v>-5.726872246696</v>
       </c>
       <c r="L24" s="14">
-        <v>-26.377952755905</v>
+        <v>-21.033210332103</v>
       </c>
       <c r="M24" s="14">
-        <v>-29.166666666666</v>
+        <v>-25.174825174825</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
         <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-60</v>
+        <v>20</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G25" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H25" s="14">
-        <v>-60</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="I25" s="15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J25" s="15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K25" s="14">
-        <v>-33.333333333333</v>
+        <v>-29.230769230769</v>
       </c>
       <c r="L25" s="14">
-        <v>-41.176470588235</v>
+        <v>-36.986301369863</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>-33.333333333333</v>
+        <v>80</v>
       </c>
       <c r="F26" s="15">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G26" s="15">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H26" s="14">
-        <v>-22.413793103448</v>
+        <v>3.571428571428</v>
       </c>
       <c r="I26" s="15">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="J26" s="15">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="K26" s="14">
-        <v>-13.294797687861</v>
+        <v>-8.196721311475</v>
       </c>
       <c r="L26" s="14">
-        <v>-23.857868020304</v>
+        <v>-21.860465116279</v>
       </c>
       <c r="M26" s="14">
-        <v>26.050420168067</v>
+        <v>36.585365853658</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
         <v>5</v>
@@ -1403,16 +1403,16 @@
         <v>150</v>
       </c>
       <c r="I27" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>28.571428571428</v>
+        <v>25</v>
       </c>
       <c r="L27" s="14">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I28" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K28" s="14">
-        <v>42.857142857142</v>
+        <v>31.25</v>
       </c>
       <c r="L28" s="14">
-        <v>33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
       </c>
       <c r="H29" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="15">
         <v>5</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="14">
-        <v>-16.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="N29" s="14">
         <v>-64.285714285714</v>
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
       </c>
       <c r="H30" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="15">
         <v>4</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="14">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N30" s="14">
         <v>-71.428571428571</v>

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>3</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
-        <v>-25</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I16" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" s="15">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K16" s="14">
-        <v>-40.350877192982</v>
+        <v>-40</v>
       </c>
       <c r="L16" s="14">
-        <v>-52.777777777777</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="M16" s="14">
-        <v>-49.253731343283</v>
+        <v>-49.295774647887</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.821428571428</v>
+        <v>-85.123966942148</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="F17" s="15">
+        <v>25</v>
+      </c>
+      <c r="G17" s="15">
+        <v>25</v>
+      </c>
+      <c r="H17" s="14">
         <v>0</v>
       </c>
-      <c r="F17" s="15">
-        <v>27</v>
-      </c>
-      <c r="G17" s="15">
-        <v>26</v>
-      </c>
-      <c r="H17" s="14">
-        <v>3.846153846153</v>
-      </c>
       <c r="I17" s="15">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J17" s="15">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="K17" s="14">
-        <v>4.651162790697</v>
+        <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>-33.823529411764</v>
+        <v>-35.862068965517</v>
       </c>
       <c r="M17" s="14">
-        <v>30.434782608695</v>
+        <v>22.368421052631</v>
       </c>
       <c r="N17" s="14">
-        <v>-47.368421052631</v>
+        <v>-48.044692737430</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H18" s="14">
-        <v>16.666666666666</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K18" s="14">
-        <v>-18.421052631578</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="14">
-        <v>14.814814814814</v>
+        <v>13.793103448275</v>
       </c>
       <c r="M18" s="14">
-        <v>3.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N18" s="14">
-        <v>-77.697841726618</v>
+        <v>-78.980891719745</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
         <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G19" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" s="14">
-        <v>-14.285714285714</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I19" s="15">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J19" s="15">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="K19" s="14">
-        <v>-23.728813559322</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L19" s="14">
-        <v>-40.397350993377</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M19" s="14">
-        <v>55.172413793103</v>
+        <v>68.965517241379</v>
       </c>
       <c r="N19" s="14">
-        <v>9.756097560975</v>
+        <v>11.363636363636</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" s="14">
-        <v>-55.555555555555</v>
+        <v>-70</v>
       </c>
       <c r="I20" s="15">
         <v>12</v>
       </c>
       <c r="J20" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K20" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="14">
-        <v>-69.230769230769</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="M20" s="14">
         <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-86.206896551724</v>
+        <v>-87.368421052631</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>15</v>
+      </c>
+      <c r="D21" s="17">
         <v>27</v>
       </c>
-      <c r="D21" s="17">
-        <v>32</v>
-      </c>
       <c r="E21" s="18">
-        <v>-15.625</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G21" s="17">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.421052631578</v>
+        <v>-14</v>
       </c>
       <c r="I21" s="17">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="J21" s="17">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.266055045871</v>
+        <v>-21.186440677966</v>
       </c>
       <c r="L21" s="18">
-        <v>-39.030023094688</v>
+        <v>-41.014799154334</v>
       </c>
       <c r="M21" s="18">
-        <v>7.317073170731</v>
+        <v>7.307692307692</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.179916317991</v>
+        <v>-64.092664092664</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,10 +1192,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="15">
         <v>4</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G23" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H23" s="14">
-        <v>10</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J23" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K23" s="14">
-        <v>-27.659574468085</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L23" s="14">
-        <v>-39.285714285714</v>
+        <v>-38.983050847457</v>
       </c>
       <c r="M23" s="14">
-        <v>41.666666666666</v>
+        <v>44</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>80</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F24" s="15">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G24" s="15">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H24" s="14">
-        <v>23.636363636363</v>
+        <v>34.615384615384</v>
       </c>
       <c r="I24" s="15">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="J24" s="15">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="K24" s="14">
-        <v>-5.726872246696</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="L24" s="14">
-        <v>-21.033210332103</v>
+        <v>-21.088435374149</v>
       </c>
       <c r="M24" s="14">
-        <v>-25.174825174825</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="14">
-        <v>20</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G25" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H25" s="14">
-        <v>-38.888888888888</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I25" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J25" s="15">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K25" s="14">
-        <v>-29.230769230769</v>
+        <v>-30.882352941176</v>
       </c>
       <c r="L25" s="14">
-        <v>-36.986301369863</v>
+        <v>-38.961038961039</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E26" s="14">
-        <v>80</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F26" s="15">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G26" s="15">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H26" s="14">
-        <v>3.571428571428</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I26" s="15">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="J26" s="15">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="K26" s="14">
-        <v>-8.196721311475</v>
+        <v>-10</v>
       </c>
       <c r="L26" s="14">
-        <v>-21.860465116279</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="M26" s="14">
-        <v>36.585365853658</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
         <v>10</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H28" s="14">
-        <v>-57.142857142857</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I28" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K28" s="14">
-        <v>31.25</v>
+        <v>10</v>
       </c>
       <c r="L28" s="14">
-        <v>40</v>
+        <v>46.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1488,16 +1488,16 @@
         <v>5</v>
       </c>
       <c r="J29" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="14">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L29" s="14">
         <v>0</v>
       </c>
       <c r="M29" s="14">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N29" s="14">
         <v>-64.285714285714</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1529,16 +1529,16 @@
         <v>4</v>
       </c>
       <c r="J30" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L30" s="14">
         <v>0</v>
       </c>
       <c r="M30" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="14">
         <v>-71.428571428571</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="15">
         <v>7</v>
       </c>
       <c r="K15" s="14">
+        <v>14.285714285714</v>
+      </c>
+      <c r="L15" s="14">
+        <v>100</v>
+      </c>
+      <c r="M15" s="14">
+        <v>14.285714285714</v>
+      </c>
+      <c r="N15" s="14">
         <v>0</v>
-      </c>
-      <c r="L15" s="14">
-        <v>133.333333333333</v>
-      </c>
-      <c r="M15" s="14">
-        <v>0</v>
-      </c>
-      <c r="N15" s="14">
-        <v>-12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>-38.461538461538</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J16" s="15">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K16" s="14">
-        <v>-40</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="L16" s="14">
-        <v>-53.846153846153</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="14">
-        <v>-49.295774647887</v>
+        <v>-43.661971830985</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.123966942148</v>
+        <v>-84.555984555984</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>-57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G17" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I17" s="15">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J17" s="15">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K17" s="14">
         <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>-35.862068965517</v>
+        <v>-34.415584415584</v>
       </c>
       <c r="M17" s="14">
-        <v>22.368421052631</v>
+        <v>29.487179487179</v>
       </c>
       <c r="N17" s="14">
-        <v>-48.044692737430</v>
+        <v>-46.842105263157</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>-13.333333333333</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I18" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J18" s="15">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K18" s="14">
-        <v>-25</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="L18" s="14">
-        <v>13.793103448275</v>
+        <v>20</v>
       </c>
       <c r="M18" s="14">
         <v>0</v>
       </c>
       <c r="N18" s="14">
-        <v>-78.980891719745</v>
+        <v>-78.313253012048</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
         <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F19" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G19" s="15">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H19" s="14">
-        <v>-5.555555555555</v>
+        <v>16.129032258064</v>
       </c>
       <c r="I19" s="15">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J19" s="15">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K19" s="14">
-        <v>-22.222222222222</v>
+        <v>-20.149253731343</v>
       </c>
       <c r="L19" s="14">
-        <v>-41.666666666666</v>
+        <v>-39.548022598870</v>
       </c>
       <c r="M19" s="14">
-        <v>68.965517241379</v>
+        <v>72.580645161290</v>
       </c>
       <c r="N19" s="14">
-        <v>11.363636363636</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H20" s="14">
-        <v>-70</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I20" s="15">
         <v>12</v>
       </c>
       <c r="J20" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K20" s="14">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L20" s="14">
-        <v>-72.727272727272</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N20" s="14">
-        <v>-87.368421052631</v>
+        <v>-88.118811881188</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-44.444444444444</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G21" s="17">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>-14</v>
+        <v>-16.037735849056</v>
       </c>
       <c r="I21" s="17">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="J21" s="17">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.186440677966</v>
+        <v>-20.418848167539</v>
       </c>
       <c r="L21" s="18">
-        <v>-41.014799154334</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="M21" s="18">
-        <v>7.307692307692</v>
+        <v>11.764705882352</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.092664092664</v>
+        <v>-63.461538461538</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="15">
         <v>1</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>0</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="15">
         <v>4</v>
       </c>
       <c r="E23" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F23" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G23" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H23" s="14">
-        <v>-33.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J23" s="15">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K23" s="14">
-        <v>-29.411764705882</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L23" s="14">
-        <v>-38.983050847457</v>
+        <v>-34.426229508196</v>
       </c>
       <c r="M23" s="14">
-        <v>44</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>38.461538461538</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G24" s="15">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H24" s="14">
-        <v>34.615384615384</v>
+        <v>17.460317460317</v>
       </c>
       <c r="I24" s="15">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="J24" s="15">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="K24" s="14">
-        <v>-3.333333333333</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="L24" s="14">
-        <v>-21.088435374149</v>
+        <v>-21.153846153846</v>
       </c>
       <c r="M24" s="14">
-        <v>-23.684210526315</v>
+        <v>-23.125</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F25" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G25" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H25" s="14">
-        <v>-47.058823529411</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J25" s="15">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.882352941176</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L25" s="14">
-        <v>-38.961038961039</v>
+        <v>-36.708860759493</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>6</v>
+      </c>
+      <c r="D26" s="15">
         <v>12</v>
       </c>
-      <c r="D26" s="15">
-        <v>17</v>
-      </c>
       <c r="E26" s="14">
-        <v>-29.411764705882</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G26" s="15">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H26" s="14">
-        <v>-9.090909090909</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="I26" s="15">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J26" s="15">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="K26" s="14">
-        <v>-10</v>
+        <v>-12.264150943396</v>
       </c>
       <c r="L26" s="14">
-        <v>-21.739130434782</v>
+        <v>-23.140495867768</v>
       </c>
       <c r="M26" s="14">
-        <v>42.857142857142</v>
+        <v>32.857142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="15">
         <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="L27" s="14">
-        <v>100</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
         <v>4</v>
       </c>
-      <c r="E28" s="14">
-        <v>-75</v>
-      </c>
-      <c r="F28" s="15">
-        <v>3</v>
-      </c>
       <c r="G28" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H28" s="14">
-        <v>-72.727272727272</v>
+        <v>-60</v>
       </c>
       <c r="I28" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="15">
         <v>20</v>
       </c>
       <c r="K28" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L28" s="14">
-        <v>46.666666666666</v>
+        <v>27.777777777777</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="15">
+      <c r="C29" s="15">
         <v>1</v>
       </c>
-      <c r="E29" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
       </c>
       <c r="H29" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="15">
         <v>4</v>
       </c>
       <c r="K29" s="14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L29" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M29" s="14">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="14">
-        <v>-64.285714285714</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="15">
+      <c r="C30" s="15">
         <v>1</v>
       </c>
-      <c r="E30" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
       </c>
       <c r="H30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="15">
         <v>4</v>
       </c>
       <c r="K30" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L30" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M30" s="14">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="N30" s="14">
-        <v>-71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-025pct.xlsx
+++ b/data/source/weekly/cs-en-us-025pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>8</v>
@@ -920,7 +920,7 @@
         <v>14.285714285714</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M15" s="14">
         <v>14.285714285714</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-37.5</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I16" s="15">
         <v>40</v>
       </c>
       <c r="J16" s="15">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K16" s="14">
-        <v>-39.393939393939</v>
+        <v>-40.298507462686</v>
       </c>
       <c r="L16" s="14">
-        <v>-50</v>
+        <v>-51.219512195122</v>
       </c>
       <c r="M16" s="14">
-        <v>-43.661971830985</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.555984555984</v>
+        <v>-85.815602836879</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F17" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G17" s="15">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H17" s="14">
-        <v>-6.896551724137</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="I17" s="15">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J17" s="15">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>0.909090909090</v>
       </c>
       <c r="L17" s="14">
-        <v>-34.415584415584</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="M17" s="14">
-        <v>29.487179487179</v>
+        <v>42.307692307692</v>
       </c>
       <c r="N17" s="14">
-        <v>-46.842105263157</v>
+        <v>-44.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H18" s="14">
-        <v>-29.411764705882</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K18" s="14">
-        <v>-23.404255319148</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="M18" s="14">
-        <v>0</v>
+        <v>5.555555555555</v>
       </c>
       <c r="N18" s="14">
-        <v>-78.313253012048</v>
+        <v>-78.888888888888</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>12.5</v>
+        <v>-70</v>
       </c>
       <c r="F19" s="15">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G19" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H19" s="14">
-        <v>16.129032258064</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="I19" s="15">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J19" s="15">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K19" s="14">
-        <v>-20.149253731343</v>
+        <v>-22.916666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>-39.548022598870</v>
+        <v>-40.957446808510</v>
       </c>
       <c r="M19" s="14">
-        <v>72.580645161290</v>
+        <v>65.671641791044</v>
       </c>
       <c r="N19" s="14">
-        <v>7</v>
+        <v>2.777777777777</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,20 +1100,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H20" s="14">
-        <v>-83.333333333333</v>
+        <v>-90</v>
       </c>
       <c r="I20" s="15">
         <v>12</v>
@@ -1128,10 +1128,10 @@
         <v>-73.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.118811881188</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F21" s="17">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G21" s="17">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.037735849056</v>
+        <v>-23.148148148148</v>
       </c>
       <c r="I21" s="17">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="J21" s="17">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.418848167539</v>
+        <v>-20.595533498759</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.709677419354</v>
+        <v>-39.163498098859</v>
       </c>
       <c r="M21" s="18">
-        <v>11.764705882352</v>
+        <v>12.676056338028</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.461538461538</v>
+        <v>-64.205816554809</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
       </c>
       <c r="J22" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="14">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="L22" s="14">
         <v>-40</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="14">
+        <v>-20</v>
+      </c>
+      <c r="F23" s="15">
+        <v>15</v>
+      </c>
+      <c r="G23" s="15">
+        <v>17</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-11.764705882352</v>
+      </c>
+      <c r="I23" s="15">
+        <v>45</v>
+      </c>
+      <c r="J23" s="15">
+        <v>60</v>
+      </c>
+      <c r="K23" s="14">
         <v>-25</v>
       </c>
-      <c r="F23" s="15">
-        <v>12</v>
-      </c>
-      <c r="G23" s="15">
-        <v>14</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="I23" s="15">
-        <v>40</v>
-      </c>
-      <c r="J23" s="15">
-        <v>55</v>
-      </c>
-      <c r="K23" s="14">
-        <v>-27.272727272727</v>
-      </c>
       <c r="L23" s="14">
-        <v>-34.426229508196</v>
+        <v>-27.419354838709</v>
       </c>
       <c r="M23" s="14">
-        <v>53.846153846153</v>
+        <v>55.172413793103</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
-        <v>-45.833333333333</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="F24" s="15">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G24" s="15">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="H24" s="14">
-        <v>17.460317460317</v>
+        <v>-5.333333333333</v>
       </c>
       <c r="I24" s="15">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="J24" s="15">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="K24" s="14">
-        <v>-6.818181818181</v>
+        <v>-10.104529616724</v>
       </c>
       <c r="L24" s="14">
-        <v>-21.153846153846</v>
+        <v>-21.100917431192</v>
       </c>
       <c r="M24" s="14">
-        <v>-23.125</v>
+        <v>-24.117647058823</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,13 +1303,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-57.142857142857</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="15">
         <v>12</v>
@@ -1321,16 +1321,16 @@
         <v>-40</v>
       </c>
       <c r="I25" s="15">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J25" s="15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K25" s="14">
-        <v>-33.333333333333</v>
+        <v>-35</v>
       </c>
       <c r="L25" s="14">
-        <v>-36.708860759493</v>
+        <v>-35</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F26" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G26" s="15">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H26" s="14">
-        <v>-13.725490196078</v>
+        <v>-8</v>
       </c>
       <c r="I26" s="15">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="J26" s="15">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="K26" s="14">
-        <v>-12.264150943396</v>
+        <v>-12.107623318385</v>
       </c>
       <c r="L26" s="14">
-        <v>-23.140495867768</v>
+        <v>-22.834645669291</v>
       </c>
       <c r="M26" s="14">
-        <v>32.857142857142</v>
+        <v>28.947368421052</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
         <v>11</v>
@@ -1412,7 +1412,7 @@
         <v>37.5</v>
       </c>
       <c r="L27" s="14">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="14">
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-60</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I28" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="14">
-        <v>15</v>
+        <v>19.047619047619</v>
       </c>
       <c r="L28" s="14">
-        <v>27.777777777777</v>
+        <v>38.888888888888</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
